--- a/www/download/COUNTRY.CHN.EXI382.xlsx
+++ b/www/download/COUNTRY.CHN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37621595092025</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37555828220859</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37555828220859</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37555828220859</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37555828220859</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1414.195</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>563.524</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>571.43</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>576.251</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>560.604</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>563.269</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>561.639</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>559.975</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>562.223</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>554.292</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>557.997</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>571.855</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>588.672</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>602.132</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>586.445</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>565.957</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>600.768</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>627.379</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>635.611</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>667.071</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>718.124</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>873.528</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>864.527</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>932.682</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>974.65</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1074.382</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1130.075</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>420.435</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>137.543</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>140.97</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>138.781</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>116.164</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>111.719</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>105.549</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>100.925</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>98.314</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>98.068</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>98.664</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>100.987</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>103.689</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>106.082</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>86.274</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>94.359</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>113.472</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>125.843</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>132.875</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>162.417</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>180.016</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>244.74</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>248.214</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>259.001</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>285.377</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>313.784</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>330.596</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3226007.93</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1322267.187</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1340365.835</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1352111.089</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1313778.722</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1320105.998</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1316373.231</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1313002.56</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1319761.626</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1301219.734</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1289135.599</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1366161.383</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1387438.056</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1334233.856</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1273554.479</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1239195.747</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1316292.774</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1393284.294</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1423831.754</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1504344.065</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1618832.304</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1969463.893</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1954212.4</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>2118014.253</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2220813.821</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>2447788.289</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2577679.32</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>841217.738</t>
+          <t>3396967084024.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-669720.383</t>
+          <t>1962789398788.91</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-674520.302</t>
+          <t>2025686388613.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-697467.738</t>
+          <t>1850160237740.61</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-770390.921</t>
+          <t>1921103062591.31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-798927.927</t>
+          <t>1889692318484.57</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-825401.076</t>
+          <t>1904404601449.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-844791.149</t>
+          <t>1929598496676.09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-864237.414</t>
+          <t>1995902019174.54</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-846554.307</t>
+          <t>2144757906610.07</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-830577.541</t>
+          <t>2206717964092.73</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-868927.605</t>
+          <t>2273641262615.86</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-878847.702</t>
+          <t>2345454956747.01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-825416.092</t>
+          <t>2206680983918.54</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-860126.586</t>
+          <t>2177401748911.31</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-789376.378</t>
+          <t>2217053783164.64</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-782109.768</t>
+          <t>2370530861542.66</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-798117.581</t>
+          <t>2404046123061</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-794268.834</t>
+          <t>2566027368403.55</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>357367.698</t>
+          <t>2742098168184.91</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>368348.759</t>
+          <t>2909745100257.19</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>474821.803</t>
+          <t>3343837281110.86</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>479972.745</t>
+          <t>3349551944829.03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>503335.512</t>
+          <t>3535514560729.88</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>566591.681</t>
+          <t>3716688100745.1</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>626464.452</t>
+          <t>3993373080273.31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>658802.493</t>
+          <t>4244868635351.73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>486225640607.153</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>285656363947.502</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>520725392084.012</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>852960666040.069</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>579612905011.335</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>623714486384.807</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>679222138176.186</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>771317284664.829</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>766502591104.553</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>551206205484.72</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>502044474413.96</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>704315107454.83</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>674904768325.599</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>652973533007.94</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>735162029090.686</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>643064339842.4</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>681322999458.945</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>682928634308.938</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>647427866620.565</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>488130228648.836</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>433045901333.31</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>665186966551.494</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>547401746892.965</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>699770430285.919</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>520043517413.909</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>780099783008.43</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>816107336594.682</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2761388781.94337</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>140495326.514235</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>142176403.919333</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>96034271.6502948</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>77302354.335201</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>63351635.3675686</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>60594502.854469</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>59721653.6722051</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>82118981.910322</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65184652.0325339</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>88661974.4334624</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>57896113.7455265</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>48805858.4751934</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>40991895.6419429</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>33322170.5663072</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>26001839.8386411</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>23699883.1691996</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>19104286.9246863</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>18614641.2094337</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>43692076.5214504</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>38029389.6143712</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>44179470.8698168</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>39448152.384626</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>37670890.9934644</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>37936047.8839712</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>36560735.3930219</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>36339211.7492255</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9076904.34094569</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8877776.24502017</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>9781525.60421033</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10069200.8242276</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10319802.0668634</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>12378016.1836753</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12403670.9253236</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11974673.4412206</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>11010107.9016166</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10543388.9234679</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>11201114.961044</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>12491671.2427564</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>13033317.481732</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>12477162.9472845</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>11851392.1550353</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>13151910.6309133</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>14617829.4020813</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>16743701.6640588</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>16422837.4400541</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>17832804.2168469</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>21430417.034102</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>23594220.8491387</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>24772041.297782</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>25317883.3091822</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>28683802.2393646</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>30002409.2293248</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30920545.9517358</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12662543.4756209</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>14915378.8055018</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16765844.6186556</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>15742904.3421138</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>17242466.4172659</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20274156.399772</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20515677.4926744</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20150096.0963002</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>19146252.0676544</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>20105865.2507496</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>22177011.9144426</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>24442348.1777291</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>26123471.2584072</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>24696091.2582725</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>24419885.2693176</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>28673954.1316713</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>31917564.2079512</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>35727368.7249143</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>37250966.0590479</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>41203421.9922845</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>49390441.4684687</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>51733970.4091592</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>54788924.7948837</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>56244573.216777</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>62997382.8750115</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>64390972.5948612</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>67199072.7950901</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.730097444860332</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-3.34449663233228</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-2.29534743604659</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-1.81770211219485</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-2.32914728843925</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-2.28091930625369</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.21521521435837</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-2.09525764050083</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-2.12750749123171</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-2.53582143781362</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-2.65439036350253</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-2.23371995829924</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-2.30218031260992</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-2.2640881292031</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-2.16998233347902</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-2.22752317230352</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-2.14792802981987</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-2.16866908257248</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-2.22680668341615</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.267884518248796</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.149400196203255</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.286182943291607</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.123180100153894</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.280713373363038</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.089508208477701</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.196943178980543</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.192750189265619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1156.48153789136</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2076.84379085618</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3693.87643804752</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6146.10879358542</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4989.62158585006</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5582.90639504125</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6435.12960486262</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7642.49505240135</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7796.51412170581</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5620.68172925757</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5088.40033056492</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6974.32149570175</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6508.93941712342</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6155.37757661999</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>8521.2070914328</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>6815.10385202429</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6004.33234534903</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>5426.81327991284</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>4872.43973961561</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>3005.40903051358</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2405.59132521181</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2717.93502627076</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2205.35858775161</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2701.80506719381</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1822.30534059015</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2486.10494833944</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2468.59131511337</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>-440002081171.271</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>-85589895278.8563</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>-109968261271.675</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>-77674654469.6411</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-55924598550.4222</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>-60029507352.5761</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>-43417188352.3068</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>-41043901580.0814</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>-55534246896.3469</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>-64531522798.84</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>-68885745302.4057</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>-47506900915.485</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>-53359468592.5996</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>-6140443865.2521</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>22950359110.6215</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>33876983745.6658</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>44931629248.0828</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>69758270188.8492</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>3.678</t>
+          <t>86230627706.3973</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>111342378170.022</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.874</t>
+          <t>127713081952.938</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>4.916</t>
+          <t>112048823990.776</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>110432100659.631</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.645</t>
+          <t>135179696540.581</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>110829691570.124</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>6.503</t>
+          <t>140630457563.976</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>152684793794.873</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-424584363367.253</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-82590447477.0944</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-106077233483.189</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-73564933062.2424</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-51131482667.3885</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-54566747923.5113</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-37853677146.4582</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-34570735616.9206</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-49835392373.9339</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-56594714600.9758</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-59574523213.5224</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-38130029677.2313</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-43935863590.8651</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6235299290.84167</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>34874590519.7526</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>46590461697.0273</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>60753866714.5378</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>87299326122.8987</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>105787779090.218</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>130269621051.673</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>149761632468.95</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>136413733614.242</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>124819201417.839</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>150418099317.116</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>124810030415.432</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>156012706212.845</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>163128004996.61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-15417717804.0184</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-2999447801.76189</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-3891027788.48574</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-4109721407.39876</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-4793115883.03363</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-5462759429.06478</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-5563511205.84862</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-6473165963.16076</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-5698854522.41305</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-7936808197.86423</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-9311222088.88335</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-9376871238.25375</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-9423605001.73457</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-12375743156.0938</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-11924231409.1311</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-12713477951.3615</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-15822237466.4551</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-17541055934.0495</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-19557151383.8205</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-18927242881.6506</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-22048550516.0116</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-24364909623.4663</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-14387100758.2079</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-15238402776.535</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-13980338845.3079</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-15382248648.8691</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-10443211201.7374</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>2000.82575373399</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>-4869.15327354251</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.141</t>
+          <t>-4784.85337309776</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>-5025.68614229417</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>-6631.94200117055</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.368</t>
+          <t>-7151.25258641554</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>-7820.06740219699</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.049</t>
+          <t>-8370.50109863241</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.978</t>
+          <t>-8790.62807771716</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.285</t>
+          <t>-8632.36349492112</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>-8418.20047252969</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>6.488</t>
+          <t>-8604.35962484265</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>7.769</t>
+          <t>-8475.81276494881</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9.245</t>
+          <t>-7780.93972536828</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>10.607</t>
+          <t>-9969.66175689257</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>13.487</t>
+          <t>-8365.69790001481</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>16.004</t>
+          <t>-6892.54139958024</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>19.213</t>
+          <t>-6342.14889712792</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>20.788</t>
+          <t>-5977.5416371029</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>2200.30648023387</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>27.186</t>
+          <t>2046.19550924031</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>27.389</t>
+          <t>1940.10838077724</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>29.346</t>
+          <t>1933.70229603712</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>32.301</t>
+          <t>1943.37225261248</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>1985.41662692572</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>37.037</t>
+          <t>1996.48353653421</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>39.076</t>
+          <t>1992.7698719058</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>2281.16128033744</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>2346.42776615385</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>2345.63475785882</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>2346.39424000479</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2343.50704756281</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>2343.65273974163</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>2343.80624610995</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>2344.75294331127</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>2347.39676573548</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>2347.53433043692</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>2310.29002993396</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>2389.00130047097</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>2356.89573653806</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>2215.84870525145</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>2171.6512967956</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>2189.55657687319</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>2191.01642320821</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>2220.7998411806</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>3.678</t>
+          <t>2240.10070675395</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>2255.14934179541</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>4.874</t>
+          <t>2254.25196441658</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>4.916</t>
+          <t>2254.60751837102</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>2260.44177402421</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>5.645</t>
+          <t>2270.88568461264</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>2278.57484107887</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>6.503</t>
+          <t>2278.32312220965</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>2280.98089820693</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>137763.156677059</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>166191.273210355</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>235728.789670847</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>238709.436185764</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>267645.429772711</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>390914.748094042</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>430729.425069141</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>494140.490821568</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>542145.660545813</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>613650.414635895</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>774491.582301071</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>984358.296878157</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1149990.36757974</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1279652.83920338</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1119554.19381275</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1532359.24142523</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1841630.98402407</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2146189.56803787</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2233995.85699301</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2345914.41930111</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2695435.1722628</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2527113.73550126</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2732175.65475985</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2859016.9504528</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>3037177.38460517</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>3131066.74289795</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3253766.90054918</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>496703043216.109</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>118580373795.236</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>151609144793.035</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>120293011485.072</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>104679305144.125</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>120154888705.125</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>119397456102.425</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>132425623339.517</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>152348765318.424</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>180423048833.907</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>204952620402.124</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>202198307242.999</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>198948508046.642</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>183929505313.597</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>146337821861.809</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>164006217013.933</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>174943079233.967</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>175338536568.229</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>194528485615.663</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>200479002395.879</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>195352186685.184</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>213092828133.346</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>222553273613.579</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>222809253911.301</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>239706147425.396</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>240105511211.368</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>249471828398.686</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>125844.5967388</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>148184.775141775</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>186525.579309266</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>187737.565451953</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>230147.880679231</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>350269.211135897</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>389853.250130273</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>442673.127945064</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>500993.603806361</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>560137.160142652</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>644801.217869019</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>768504.388211319</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>857876.50673102</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>970260.530728882</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>913941.01612822</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1312173.83281347</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1670306.6839908</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1910340.24115808</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2003990.09509995</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2128790.45939961</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2274377.34377386</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2225045.58320359</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2481515.3699646</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2740475.46362383</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2787790.42743401</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2859936.10045992</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3008837.34708074</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3226007.93</t>
+          <t>49948785100.3959</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1322267.187</t>
+          <t>29332673632.703</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1340365.835</t>
+          <t>32430646895.523</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1352111.089</t>
+          <t>33015342175.0864</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1313778.722</t>
+          <t>41876010215.4259</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1320105.998</t>
+          <t>53819609240.2571</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1316373.231</t>
+          <t>69387799599.8522</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1313002.56</t>
+          <t>82769505181.6712</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1319761.626</t>
+          <t>89823703438.6001</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1301219.734</t>
+          <t>106077738767.392</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1289135.599</t>
+          <t>114376085868.209</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1366161.383</t>
+          <t>122574136392.946</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1387438.056</t>
+          <t>109313637966.854</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1334233.856</t>
+          <t>135390140771.045</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1273554.479</t>
+          <t>139023687437.68</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1239195.747</t>
+          <t>170733895899.268</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1316292.774</t>
+          <t>200118317421.274</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1393284.294</t>
+          <t>219381864188.326</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1423831.754</t>
+          <t>254411135210.861</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1504344.065</t>
+          <t>288739780791.622</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>1618832.304</t>
+          <t>282363762741.649</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1969463.893</t>
+          <t>293105351542.015</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1954212.4</t>
+          <t>308841084565.546</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2118014.253</t>
+          <t>346207146908.785</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2220813.821</t>
+          <t>327774938299.942</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2447788.289</t>
+          <t>354425091598.11</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2577679.32</t>
+          <t>378291893030.022</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>841217.738</t>
+          <t>11918.5599382581</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-669720.383</t>
+          <t>18006.4980685801</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-674520.302</t>
+          <t>49203.2103615811</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-697467.738</t>
+          <t>50971.8707338105</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-770390.921</t>
+          <t>37497.5490934805</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-798927.927</t>
+          <t>40645.5369581446</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-825401.076</t>
+          <t>40876.1749388676</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-844791.149</t>
+          <t>51467.3628765044</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-864237.414</t>
+          <t>41152.0567394516</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-846554.307</t>
+          <t>53513.2544932429</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-830577.541</t>
+          <t>129690.364432052</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-868927.605</t>
+          <t>215853.908666838</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-878847.702</t>
+          <t>292113.860848717</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-825416.092</t>
+          <t>309392.308474501</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-860126.586</t>
+          <t>205613.177684529</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-789376.378</t>
+          <t>220185.408611759</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-782109.768</t>
+          <t>171324.300033266</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-798117.581</t>
+          <t>235849.32687979</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-794268.834</t>
+          <t>230005.761893061</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>357367.698</t>
+          <t>217123.959901503</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>368348.759</t>
+          <t>421057.828488932</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>474821.803</t>
+          <t>302068.152297666</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>479972.745</t>
+          <t>250660.284795247</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>503335.512</t>
+          <t>118541.486828973</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>566591.681</t>
+          <t>249386.957171159</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>626464.452</t>
+          <t>271130.642438022</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>658802.493</t>
+          <t>244929.553468442</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3741064.2</t>
+          <t>446754258115.713</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2279346.173</t>
+          <t>89247700162.5331</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2283615.106</t>
+          <t>119178497897.513</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2068045.511</t>
+          <t>87277669309.9852</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2138178.139</t>
+          <t>62803294928.6994</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2091425.513</t>
+          <t>66335279464.868</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2107214.811</t>
+          <t>50009656502.573</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2133305.551</t>
+          <t>49656118157.8457</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2210005.352</t>
+          <t>62525061879.8237</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2386359.994</t>
+          <t>74345310066.515</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2464345.507</t>
+          <t>90576534533.9146</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2538942.202</t>
+          <t>79624170850.0531</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2626609.972</t>
+          <t>89634870079.7878</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2456078.904</t>
+          <t>48539364542.5515</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2426125.762</t>
+          <t>7314134424.12856</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2470597.802</t>
+          <t>-6727678885.33569</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2630860.902</t>
+          <t>-25175238187.3071</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2655536.984</t>
+          <t>-44043327620.0977</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2835402.393</t>
+          <t>-59882649595.1973</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3031748.187</t>
+          <t>-88260778395.7437</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>3218726.203</t>
+          <t>-87011576056.4643</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>3688896.938</t>
+          <t>-80012523408.6681</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>3705438.605</t>
+          <t>-86287810951.9666</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3890541.297</t>
+          <t>-123397892997.484</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>4111038.93</t>
+          <t>-88068790874.5452</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>4404802.011</t>
+          <t>-114319580386.741</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>4679006.949</t>
+          <t>-128820064631.336</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12.128</t>
+          <t>295795.21927904</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14.771</t>
+          <t>349312.23800829</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.202</t>
+          <t>506758.350457893</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15.243</t>
+          <t>510840.368846715</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>16.646</t>
+          <t>555503.251289607</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>19.474</t>
+          <t>796133.191061337</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>19.722</t>
+          <t>912021.821162586</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19.387</t>
+          <t>911652.710261706</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18.492</t>
+          <t>870431.11148803</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19.574</t>
+          <t>887244.727503673</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21.609</t>
+          <t>1118670.72989779</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>23.869</t>
+          <t>1296036.07080024</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>25.483</t>
+          <t>1503318.06406086</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>24.157</t>
+          <t>1722294.38991222</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>23.754</t>
+          <t>2074551.26520787</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>27.848</t>
+          <t>2742012.74076748</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>30.907</t>
+          <t>3373935.45739577</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>34.427</t>
+          <t>4049512.00704144</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>35.736</t>
+          <t>4560992.03378785</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>39.251</t>
+          <t>4796633.15920826</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>46.531</t>
+          <t>6118701.73433723</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>48.401</t>
+          <t>6028032.36244056</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>51.004</t>
+          <t>6306771.47743998</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>52.045</t>
+          <t>6872022.03859176</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>58.175</t>
+          <t>7535288.74389637</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>59.373</t>
+          <t>7878317.78798291</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>61.891</t>
+          <t>8341298.69494392</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2435051.483</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1168271.039</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1181825.534</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1183367.096</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1149800.897</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1153717.158</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1151393.026</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>1146709.761</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1147749.257</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1124697.519</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1114564.113</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1161982.432</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1170176</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>1114877.57</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1056730.682</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1016898.231</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1085672.312</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1126660.947</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1131284.764</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1186777.637</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1262532.772</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1525017.985</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>1514452.773</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>1591473.452</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1692272.625</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>1860677.181</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1953206.35</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7.894</t>
+          <t>383713.166167558</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.571</t>
+          <t>493808.957453354</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8.385</t>
+          <t>672931.679676664</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>8.722</t>
+          <t>857301.78752166</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8.951</t>
+          <t>833577.724720378</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>10.743</t>
+          <t>1050362.64164637</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10.776</t>
+          <t>1135291.35951842</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>10.421</t>
+          <t>1238509.09088636</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>9.604</t>
+          <t>1099208.13895123</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>9.225</t>
+          <t>988924.69602168</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>9.773</t>
+          <t>1210221.22515616</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>10.924</t>
+          <t>1457281.94853316</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>11.353</t>
+          <t>1552547.81780608</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>10.966</t>
+          <t>1850516.84746682</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10.346</t>
+          <t>2386515.92707981</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>11.462</t>
+          <t>3095247.32572743</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12.754</t>
+          <t>3812696.7655739</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>14.606</t>
+          <t>4408189.81255738</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>14.258</t>
+          <t>5101748.10240916</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>15.365</t>
+          <t>5375738.82682761</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>18.252</t>
+          <t>6758653.09040043</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>20.009</t>
+          <t>6814641.04487174</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>20.846</t>
+          <t>7459191.69926893</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>7823176.96811613</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>23.947</t>
+          <t>8467964.97717361</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>25.081</t>
+          <t>9012007.10697801</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>25.836</t>
+          <t>9532839.94794653</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>501846.797</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>296166.251</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>534517.628</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>868788.565</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>592987.93</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>635696.029</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>692342.323</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>789540.412</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>787846.99</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>569039.494</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>519687.461</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>730890.17</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>705893.701</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>678621.328</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>764589.97</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>669921.76</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>709055.95</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>704839.754</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>671460.132</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>500895.612</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>445712.076</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>697030.275</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>559591.695</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>730782.193</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>537107.389</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>816537.361</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>854400.571</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>67.62</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-326.13</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-226.19</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-180.28</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-229.92</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-225.68</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-219.22</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-207</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-209.7</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-248.77</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-259.82</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-218.89</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-224.5</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-221.63</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-212.5</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-217.83</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-210.3</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-213.23</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-218.29</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-28.65</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-17.36</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-31.88</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-14.23</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-31.12</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>5.49</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-23.28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-22.89</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3598.582</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>210.258</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>207.085</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>140.091</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>112.569</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>91.658</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>87.648</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>86.686</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>119.325</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>94.609</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>128.107</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>84.341</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>71.75</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>59.425</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>48.095</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>37.574</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>34.145</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>27.403</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>26.798</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>61.734</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>53.676</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>62.215</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>55.695</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>53.032</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>53.533</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>51.542</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>51.162</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>379663.856896977</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>468270.109422194</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>514627.970393454</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>580345.03792585</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>657784.857596886</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>745186.784239647</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>844949.183889088</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>915357.125109227</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>866172.923097043</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>980473.419289923</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1099244.55555624</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1337765.39901138</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1634165.5822859</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1911408.53362617</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2068677.82513023</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2454760.67473868</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2788817.83893832</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>3497521.35428991</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>3536034.62526196</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>4080968.28302793</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>5157181.70825565</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>5302627.46397642</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>5475263.10990024</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>6237958.46718834</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>6871291.03581932</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>7241841.31628685</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>7687273.69514433</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>841217738440.014</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-669720383279.202</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-674520301520.379</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-697467738240.095</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-770390921040.211</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-798927927200.404</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-825401076240.721</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-844791149279.511</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-864237413518.904</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-846554307039.334</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-830577540520.147</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-868927604998.697</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-878847702200.154</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-825416091759.146</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-860126586280.696</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-789376378438.614</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-782109768439.872</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-798117580520.306</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-794268833799.972</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>357367697504.568</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>368348758709.098</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>474821802624.572</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>479972744886.273</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>503335512220.654</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>566591680988.07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>626464451820.718</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>658802493004.997</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3226007929583.45</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1322267187280.25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1340365835120.12</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1352111088639.52</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1313778721839.82</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1320105997600.25</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1316373230639.41</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1313002560480.1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1319761625520.36</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1301219733840.37</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1289135598919.79</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1366161383080.44</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1387438055640.18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1334233855760.22</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1273554479079.61</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1239195747400.09</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1316292773639.89</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1393284293959.95</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1423831754280.04</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1504344064721.83</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1618832303847.31</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1969463892996.68</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1954212400428.52</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>2118014252840.92</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2220813820829.07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>2447788289194.64</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2577679319614.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2435051483171.03</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1168271039292.54</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1181825534412.65</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1183367095801.68</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1149800897169.51</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1153717157900.19</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1151393025820.42</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1146709760585.66</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1147749257375.06</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1124697518562.64</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1114564112503.65</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1161982431886.04</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1170175999506.49</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1114877569939.45</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1056730681606.87</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1016898230575.85</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1085672311979.47</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1126660946712.84</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1131284763762.14</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1186777636716.01</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1262532771675.18</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1525017984704.02</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1514452773384.58</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1591473451873.82</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1692272624700.72</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1860677180845.85</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1953206350014.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1414195461.49155</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>563523500.00002</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>571429900.000141</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>576250600.000092</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>560603700.000012</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>563268599.999922</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>561639099.999931</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>559974799.999981</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>562223499.999949</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>554292100.00017</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>557997299.999877</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>571854600.000057</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>588671799.999998</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>602132200.000007</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>586445200.000028</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>565957400.00002</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>600768100.000136</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>627379499.999993</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>635610599.999885</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>667070706.51213</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>718123940.62448</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>873528486.421284</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>864526758.833289</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>932682022.345919</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>974650373.90545</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1074381533.21317</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1130074925.94114</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>420435281.218323</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>137543499.99994</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>140969900.000026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>138780600.000164</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>116163699.999824</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>111718599.999955</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>105549099.999935</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>100924800.000031</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>98313500.0000294</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>98067500.000134</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>98664499.9997911</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>100986900.000078</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>103688899.999605</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>106081800.000074</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>86274400.000185</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>94358700.0000582</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>113471900.000122</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>125843399.999918</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>132875499.99985</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>162417236.287276</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>180016404.613191</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>244739833.778951</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>248214394.671774</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>259001079.975295</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>285376718.067178</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>313783930.774719</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>330596373.56668</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3226007929583.45</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1322267187280.25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1340365835120.12</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1352111088639.52</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1313778721839.82</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1320105997600.25</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1316373230639.41</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1313002560480.1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1319761625520.36</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1301219733840.37</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1289135598919.79</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1366161383080.44</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1387438055640.18</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1334233855760.22</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1273554479079.61</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1239195747400.09</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1316292773639.89</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1393284293959.95</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1423831754280.04</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1504344064721.83</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>1618832303847.31</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1969463892996.68</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1954212400428.52</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2118014252840.92</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2220813820829.07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>2447788289194.64</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2577679319614.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>841217738440.014</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-669720383279.202</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-674520301520.379</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-697467738240.095</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-770390921040.211</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-798927927200.404</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-825401076240.721</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-844791149279.511</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-864237413518.904</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-846554307039.334</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-830577540520.147</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-868927604998.697</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>-878847702200.154</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>-825416091759.146</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-860126586280.696</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>-789376378438.614</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-782109768439.872</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>-798117580520.306</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>-794268833799.972</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>357367697504.568</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>368348758709.098</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>474821802624.572</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>479972744886.273</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>503335512220.654</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>566591680988.07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>626464451820.718</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>658802493004.997</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1880349.57084244</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2333182.40799051</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2975578.83017826</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3225054.20997773</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3566544.35005527</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4680094.7290994</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5336663.19876955</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>5625834.00203726</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>5528272.44744305</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5953597.34395614</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>7298122.35822646</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>9016595.17036277</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>10797386.4434394</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>12842180.7234836</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>14732552.5935627</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18739753.3018195</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>22236825.7884525</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>26689933.5668059</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>28881540.7531505</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>30783026.2565354</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>37759817.8905316</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>38033457.2966507</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>40744701.0236384</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>44852480.40194</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>48352676.6474347</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>51427333.303337</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>54258844.7977629</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>400329.470850965</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>476778.751787288</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>663920.598646427</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>695282.449997384</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>768035.754687623</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1077282.99802718</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1232996.2925737</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1245214.72167468</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1172913.29077283</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1203124.77921863</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1453551.37880142</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1707303.85105494</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1964338.87076501</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2422618.80054288</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>3005304.78928922</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>3920481.98279141</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>4743891.51111273</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>5723822.74001907</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>6469329.28826708</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>6866163.33823258</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>8681895.99737783</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>8781656.92961192</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>9645527.18650645</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10088155.3306304</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>10907656.2223546</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11569627.1546086</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>12234705.201168</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
